--- a/exports/trend_1d/PIIND_full_report.xlsx
+++ b/exports/trend_1d/PIIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H2" t="n">
-        <v>633.5</v>
+        <v>626.95</v>
       </c>
       <c r="I2" t="n">
         <v>627.4952511768497</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>20.71</v>
+        <v>19.47</v>
       </c>
       <c r="L2" t="n">
         <v>8.529999999999999</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>17.44</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42146</v>
+        <v>42149</v>
       </c>
       <c r="H3" t="n">
-        <v>714.65</v>
+        <v>722.55</v>
       </c>
       <c r="I3" t="n">
         <v>717.1794535582109</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.99</v>
+        <v>-15.25</v>
       </c>
       <c r="L3" t="n">
-        <v>15.64</v>
+        <v>21.05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.12</v>
+        <v>5.62</v>
       </c>
       <c r="N3" t="n">
         <v>4.28</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.69</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42164</v>
+        <v>42165</v>
       </c>
       <c r="H4" t="n">
-        <v>656.25</v>
+        <v>650.7</v>
       </c>
       <c r="I4" t="n">
         <v>652.5563792264245</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.18</v>
+        <v>-9.94</v>
       </c>
       <c r="L4" t="n">
         <v>19.73</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>12.25</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42222</v>
+        <v>42223</v>
       </c>
       <c r="H5" t="n">
-        <v>690.7</v>
+        <v>718.85</v>
       </c>
       <c r="I5" t="n">
         <v>703.3025520529823</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.15</v>
+        <v>-10.47</v>
       </c>
       <c r="L5" t="n">
-        <v>7.58</v>
+        <v>11.83</v>
       </c>
       <c r="M5" t="n">
         <v>3.16</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.48</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>691.8</v>
+        <v>627</v>
       </c>
       <c r="I6" t="n">
         <v>648.8999185232557</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.76</v>
+        <v>-12.78</v>
       </c>
       <c r="L6" t="n">
-        <v>7.84</v>
+        <v>17.21</v>
       </c>
       <c r="M6" t="n">
-        <v>1.67</v>
+        <v>2.72</v>
       </c>
       <c r="N6" t="n">
-        <v>3.36</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>4.08</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>17.54</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42374</v>
+        <v>42375</v>
       </c>
       <c r="H7" t="n">
-        <v>674.9</v>
+        <v>678.85</v>
       </c>
       <c r="I7" t="n">
         <v>675.6261554385076</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.64</v>
+        <v>-8.27</v>
       </c>
       <c r="L7" t="n">
         <v>16.17</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.91</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H8" t="n">
-        <v>654.3</v>
+        <v>620.3</v>
       </c>
       <c r="I8" t="n">
         <v>638.2973397056119</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.62</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>4.25</v>
+        <v>9.91</v>
       </c>
       <c r="M8" t="n">
-        <v>1.49</v>
+        <v>2.64</v>
       </c>
       <c r="N8" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
         <v>0.59</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>15.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42471</v>
+        <v>42472</v>
       </c>
       <c r="H9" t="n">
-        <v>583.6</v>
+        <v>613.4</v>
       </c>
       <c r="I9" t="n">
         <v>601.3371282410596</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
-        <v>5.92</v>
+        <v>1.11</v>
       </c>
       <c r="L9" t="n">
         <v>10.27</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.03</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H10" t="n">
-        <v>829.4</v>
+        <v>792.95</v>
       </c>
       <c r="I10" t="n">
         <v>805.2693447198383</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K10" t="n">
-        <v>35.21</v>
+        <v>29.27</v>
       </c>
       <c r="L10" t="n">
         <v>5.18</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>21.69</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42758</v>
+        <v>42759</v>
       </c>
       <c r="H11" t="n">
-        <v>836.05</v>
+        <v>893.65</v>
       </c>
       <c r="I11" t="n">
         <v>878.045182218978</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.44</v>
+        <v>-12.7</v>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>16.53</v>
       </c>
       <c r="M11" t="n">
         <v>2.48</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.26</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42795</v>
+        <v>42796</v>
       </c>
       <c r="H12" t="n">
-        <v>828.2</v>
+        <v>818.4</v>
       </c>
       <c r="I12" t="n">
         <v>822.8554487326454</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.32</v>
+        <v>-8.42</v>
       </c>
       <c r="L12" t="n">
-        <v>7.68</v>
+        <v>9.33</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.93</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42810</v>
+        <v>42811</v>
       </c>
       <c r="H13" t="n">
-        <v>884.55</v>
+        <v>907.25</v>
       </c>
       <c r="I13" t="n">
         <v>900.892747758247</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.08</v>
+        <v>-10.86</v>
       </c>
       <c r="L13" t="n">
-        <v>11.05</v>
+        <v>11.73</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="O13" t="n">
         <v>-1.18</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>10.24</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="H14" t="n">
-        <v>842.65</v>
+        <v>816.25</v>
       </c>
       <c r="I14" t="n">
         <v>819.8150211669964</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.12</v>
+        <v>-10.03</v>
       </c>
       <c r="L14" t="n">
-        <v>9.51</v>
+        <v>11.16</v>
       </c>
       <c r="M14" t="n">
         <v>0.61</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.86</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42998</v>
+        <v>42999</v>
       </c>
       <c r="H15" t="n">
-        <v>770.75</v>
+        <v>784</v>
       </c>
       <c r="I15" t="n">
         <v>774.9742326196683</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K15" t="n">
-        <v>5.57</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
         <v>4.97</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.65</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H16" t="n">
-        <v>914.8</v>
+        <v>890.85</v>
       </c>
       <c r="I16" t="n">
         <v>911.7580450790492</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K16" t="n">
-        <v>16.68</v>
+        <v>13.63</v>
       </c>
       <c r="L16" t="n">
         <v>8.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.48</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43313</v>
+        <v>43314</v>
       </c>
       <c r="H17" t="n">
-        <v>809.9</v>
+        <v>823.6</v>
       </c>
       <c r="I17" t="n">
         <v>816.1989538390137</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K17" t="n">
-        <v>9.09</v>
+        <v>7.55</v>
       </c>
       <c r="L17" t="n">
         <v>5.52</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>9.26</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43340</v>
+        <v>43341</v>
       </c>
       <c r="H18" t="n">
-        <v>776.1</v>
+        <v>755.5</v>
       </c>
       <c r="I18" t="n">
         <v>756.496285129781</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.77</v>
+        <v>-8.27</v>
       </c>
       <c r="L18" t="n">
-        <v>8.1</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M18" t="n">
         <v>2.14</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>13.13</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43385</v>
+        <v>43388</v>
       </c>
       <c r="H19" t="n">
-        <v>770.9</v>
+        <v>780.2</v>
       </c>
       <c r="I19" t="n">
         <v>778.6245258609284</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.04</v>
+        <v>-3.27</v>
       </c>
       <c r="L19" t="n">
         <v>7.94</v>
       </c>
       <c r="M19" t="n">
-        <v>0.98</v>
+        <v>1.69</v>
       </c>
       <c r="N19" t="n">
         <v>3.88</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.97</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H20" t="n">
-        <v>1124.6</v>
+        <v>1081.4</v>
       </c>
       <c r="I20" t="n">
         <v>1086.805601154231</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K20" t="n">
-        <v>44.14</v>
+        <v>38.61</v>
       </c>
       <c r="L20" t="n">
         <v>10.79</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>12.28</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43712</v>
+        <v>43713</v>
       </c>
       <c r="H21" t="n">
-        <v>1180.55</v>
+        <v>1199.1</v>
       </c>
       <c r="I21" t="n">
         <v>1193.09122139775</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.17</v>
+        <v>-10.88</v>
       </c>
       <c r="L21" t="n">
-        <v>10.32</v>
+        <v>12.63</v>
       </c>
       <c r="M21" t="n">
         <v>2.25</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.66</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H22" t="n">
-        <v>1509.45</v>
+        <v>1348.6</v>
       </c>
       <c r="I22" t="n">
         <v>1448.155920900349</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K22" t="n">
-        <v>25.88</v>
+        <v>12.47</v>
       </c>
       <c r="L22" t="n">
         <v>1.36</v>
@@ -1695,7 +1958,7 @@
         <v>3.98</v>
       </c>
       <c r="N22" t="n">
-        <v>3.98</v>
+        <v>10.66</v>
       </c>
       <c r="O22" t="n">
         <v>1.57</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>19.77</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43928</v>
+        <v>43929</v>
       </c>
       <c r="H23" t="n">
-        <v>1312.55</v>
+        <v>1385.4</v>
       </c>
       <c r="I23" t="n">
         <v>1378.53844227004</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n">
-        <v>2.67</v>
+        <v>-2.73</v>
       </c>
       <c r="L23" t="n">
         <v>10.42</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>28.29</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44161</v>
+        <v>44162</v>
       </c>
       <c r="H24" t="n">
-        <v>2272.65</v>
+        <v>2208.4</v>
       </c>
       <c r="I24" t="n">
         <v>2211.097823748427</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K24" t="n">
-        <v>64.04000000000001</v>
+        <v>59.41</v>
       </c>
       <c r="L24" t="n">
         <v>8.23</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>162</v>
+        <v>163</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>16.61</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H25" t="n">
-        <v>2063.6</v>
+        <v>2250.15</v>
       </c>
       <c r="I25" t="n">
         <v>2240.521588463307</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K25" t="n">
-        <v>6.56</v>
+        <v>-1.89</v>
       </c>
       <c r="L25" t="n">
         <v>20</v>
@@ -1866,7 +2165,7 @@
         <v>12.25</v>
       </c>
       <c r="N25" t="n">
-        <v>6.95</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-2.83</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.57</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44463</v>
+        <v>44466</v>
       </c>
       <c r="H26" t="n">
-        <v>3203.85</v>
+        <v>3149.2</v>
       </c>
       <c r="I26" t="n">
         <v>3180.667490914092</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K26" t="n">
-        <v>42.38</v>
+        <v>39.96</v>
       </c>
       <c r="L26" t="n">
         <v>5.65</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.98</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44544</v>
+        <v>44545</v>
       </c>
       <c r="H27" t="n">
-        <v>2952.4</v>
+        <v>3087.55</v>
       </c>
       <c r="I27" t="n">
         <v>3050.232541379845</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K27" t="n">
-        <v>6.25</v>
+        <v>1.96</v>
       </c>
       <c r="L27" t="n">
         <v>8.18</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>12.25</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44578</v>
+        <v>44579</v>
       </c>
       <c r="H28" t="n">
-        <v>2796.1</v>
+        <v>2713.1</v>
       </c>
       <c r="I28" t="n">
         <v>2784.078363764313</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.44</v>
+        <v>-12.13</v>
       </c>
       <c r="L28" t="n">
-        <v>10.53</v>
+        <v>12.38</v>
       </c>
       <c r="M28" t="n">
         <v>1.22</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.07</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44599</v>
+        <v>44600</v>
       </c>
       <c r="H29" t="n">
-        <v>2605.05</v>
+        <v>2664</v>
       </c>
       <c r="I29" t="n">
         <v>2633.138541741272</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>3.98</v>
+        <v>1.81</v>
       </c>
       <c r="L29" t="n">
         <v>3.75</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.77</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H30" t="n">
-        <v>2735.1</v>
+        <v>2620.3</v>
       </c>
       <c r="I30" t="n">
         <v>2722.212977115919</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K30" t="n">
-        <v>2.67</v>
+        <v>-1.64</v>
       </c>
       <c r="L30" t="n">
         <v>11.74</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>12.23</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H31" t="n">
-        <v>2675.95</v>
+        <v>2718.5</v>
       </c>
       <c r="I31" t="n">
         <v>2712.527341101507</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.12</v>
+        <v>-3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>4.84</v>
       </c>
       <c r="M31" t="n">
         <v>1.96</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>11.25</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H32" t="n">
-        <v>2473.3</v>
+        <v>2468.5</v>
       </c>
       <c r="I32" t="n">
         <v>2469.828447734109</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.02</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>9.5</v>
+        <v>10.17</v>
       </c>
       <c r="M32" t="n">
         <v>1.46</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>10.23</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H33" t="n">
-        <v>2703.55</v>
+        <v>2783.85</v>
       </c>
       <c r="I33" t="n">
         <v>2720.973029412655</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.52</v>
+        <v>-12.77</v>
       </c>
       <c r="L33" t="n">
-        <v>10.11</v>
+        <v>13.14</v>
       </c>
       <c r="M33" t="n">
         <v>1.17</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.94</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H34" t="n">
-        <v>3278.9</v>
+        <v>3136</v>
       </c>
       <c r="I34" t="n">
         <v>3184.620167420737</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K34" t="n">
-        <v>17.78</v>
+        <v>12.65</v>
       </c>
       <c r="L34" t="n">
         <v>2.65</v>
@@ -2379,7 +2786,7 @@
         <v>3.42</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>4.36</v>
       </c>
       <c r="O34" t="n">
         <v>2.97</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.06</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H35" t="n">
-        <v>3213.25</v>
+        <v>3241.95</v>
       </c>
       <c r="I35" t="n">
         <v>3239.505596251857</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.46</v>
+        <v>-3.38</v>
       </c>
       <c r="L35" t="n">
         <v>5.11</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.6</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44931</v>
+        <v>44932</v>
       </c>
       <c r="H36" t="n">
-        <v>3328.25</v>
+        <v>3288.15</v>
       </c>
       <c r="I36" t="n">
         <v>3293.448548046252</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K36" t="n">
-        <v>2.66</v>
+        <v>1.43</v>
       </c>
       <c r="L36" t="n">
         <v>0.68</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.64</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H37" t="n">
-        <v>3044.65</v>
+        <v>3154.05</v>
       </c>
       <c r="I37" t="n">
         <v>3149.218966483533</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>7.41</v>
+        <v>4.08</v>
       </c>
       <c r="L37" t="n">
         <v>2.03</v>
@@ -2550,7 +2993,7 @@
         <v>0.72</v>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>3.59</v>
       </c>
       <c r="O37" t="n">
         <v>-1.2</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>8.65</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45000</v>
+        <v>45001</v>
       </c>
       <c r="H38" t="n">
-        <v>2991.15</v>
+        <v>2972.3</v>
       </c>
       <c r="I38" t="n">
         <v>2988.466098713641</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.16</v>
+        <v>-5.76</v>
       </c>
       <c r="L38" t="n">
-        <v>5.77</v>
+        <v>6.6</v>
       </c>
       <c r="M38" t="n">
         <v>1.04</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45033</v>
+        <v>45034</v>
       </c>
       <c r="H39" t="n">
-        <v>3041.65</v>
+        <v>3153.3</v>
       </c>
       <c r="I39" t="n">
         <v>3141.62381089955</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.33</v>
+        <v>-6.09</v>
       </c>
       <c r="L39" t="n">
-        <v>4.72</v>
+        <v>6.38</v>
       </c>
       <c r="M39" t="n">
         <v>1.67</v>
       </c>
       <c r="N39" t="n">
-        <v>3.14</v>
+        <v>3.67</v>
       </c>
       <c r="O39" t="n">
         <v>-0.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.85</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45119</v>
+        <v>45120</v>
       </c>
       <c r="H40" t="n">
-        <v>3659.45</v>
+        <v>3610.6</v>
       </c>
       <c r="I40" t="n">
         <v>3632.690656969884</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K40" t="n">
-        <v>16.05</v>
+        <v>14.5</v>
       </c>
       <c r="L40" t="n">
         <v>4.39</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.85</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45145</v>
+        <v>45146</v>
       </c>
       <c r="H41" t="n">
-        <v>3778.35</v>
+        <v>3850.75</v>
       </c>
       <c r="I41" t="n">
         <v>3809.962652541961</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.65</v>
+        <v>-6.65</v>
       </c>
       <c r="L41" t="n">
-        <v>4.89</v>
+        <v>6.91</v>
       </c>
       <c r="M41" t="n">
         <v>0.68</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.6</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H42" t="n">
-        <v>3701.45</v>
+        <v>3628.3</v>
       </c>
       <c r="I42" t="n">
         <v>3629.469336393331</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.88</v>
+        <v>-5.78</v>
       </c>
       <c r="L42" t="n">
-        <v>6.02</v>
+        <v>6.6</v>
       </c>
       <c r="M42" t="n">
         <v>0.5</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.43</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="H43" t="n">
-        <v>3481.45</v>
+        <v>3514.5</v>
       </c>
       <c r="I43" t="n">
         <v>3500.582679947557</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K43" t="n">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="L43" t="n">
         <v>3.15</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.58</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="H44" t="n">
-        <v>3869.45</v>
+        <v>3484</v>
       </c>
       <c r="I44" t="n">
         <v>3632.167796205597</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K44" t="n">
-        <v>10.1</v>
+        <v>-0.87</v>
       </c>
       <c r="L44" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="M44" t="n">
         <v>0.06</v>
       </c>
       <c r="N44" t="n">
-        <v>1.25</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="O44" t="n">
         <v>0.95</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>15.25</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45330</v>
+        <v>45331</v>
       </c>
       <c r="H45" t="n">
-        <v>3455.75</v>
+        <v>3484.35</v>
       </c>
       <c r="I45" t="n">
         <v>3481.55483748536</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="L45" t="n">
         <v>11.76</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.86</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="H46" t="n">
-        <v>3640.9</v>
+        <v>3594.25</v>
       </c>
       <c r="I46" t="n">
         <v>3609.231122029543</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K46" t="n">
-        <v>4.49</v>
+        <v>3.15</v>
       </c>
       <c r="L46" t="n">
         <v>3.45</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45464</v>
+        <v>45467</v>
       </c>
       <c r="H47" t="n">
-        <v>3753.7</v>
+        <v>3803.1</v>
       </c>
       <c r="I47" t="n">
         <v>3780.537545949965</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.44</v>
+        <v>-5.81</v>
       </c>
       <c r="L47" t="n">
-        <v>5.89</v>
+        <v>6.42</v>
       </c>
       <c r="M47" t="n">
         <v>2.24</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.26</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H48" t="n">
-        <v>4400.1</v>
+        <v>4319</v>
       </c>
       <c r="I48" t="n">
         <v>4396.431288146933</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K48" t="n">
-        <v>15.7</v>
+        <v>13.57</v>
       </c>
       <c r="L48" t="n">
         <v>3.11</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>10.63</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45726</v>
+        <v>45727</v>
       </c>
       <c r="H49" t="n">
-        <v>3253.65</v>
+        <v>3353.9</v>
       </c>
       <c r="I49" t="n">
         <v>3276.219606149373</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K49" t="n">
-        <v>24.67</v>
+        <v>22.35</v>
       </c>
       <c r="L49" t="n">
         <v>9.17</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="H50" t="n">
-        <v>4023.8</v>
+        <v>3919.1</v>
       </c>
       <c r="I50" t="n">
         <v>3992.124868011408</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K50" t="n">
-        <v>19.97</v>
+        <v>16.85</v>
       </c>
       <c r="L50" t="n">
         <v>9.029999999999999</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.25</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H51" t="n">
-        <v>3683.3</v>
+        <v>3750.1</v>
       </c>
       <c r="I51" t="n">
         <v>3748.364629794203</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K51" t="n">
-        <v>6.02</v>
+        <v>4.31</v>
       </c>
       <c r="L51" t="n">
         <v>2.77</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.85</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H52" t="n">
-        <v>3560.5</v>
+        <v>3542.6</v>
       </c>
       <c r="I52" t="n">
         <v>3554.321750436396</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.06</v>
+        <v>-5.53</v>
       </c>
       <c r="L52" t="n">
         <v>6.38</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.47</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H53" t="n">
-        <v>2909.4</v>
+        <v>3042.1</v>
       </c>
       <c r="I53" t="n">
         <v>3030.913137903035</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K53" t="n">
-        <v>17.87</v>
+        <v>14.13</v>
       </c>
       <c r="L53" t="n">
         <v>1.11</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>6</v>
+      </c>
+      <c r="U53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>11.63</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="H54" t="n">
-        <v>2901.2</v>
+        <v>2740.5</v>
       </c>
       <c r="I54" t="n">
         <v>2886.200362575159</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.63</v>
+        <v>-9.91</v>
       </c>
       <c r="L54" t="n">
-        <v>5.98</v>
+        <v>11.25</v>
       </c>
       <c r="M54" t="n">
         <v>5.59</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>14.57</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H55" t="n">
-        <v>2697.6</v>
+        <v>2742.6</v>
       </c>
       <c r="I55" t="n">
         <v>2724.132264597079</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K55" t="n">
-        <v>1.57</v>
+        <v>-0.08</v>
       </c>
       <c r="L55" t="n">
         <v>6.62</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.77</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H56" t="n">
-        <v>2730</v>
+        <v>2483</v>
       </c>
       <c r="I56" t="n">
         <v>2630.97353813768</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.46</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>2.53</v>
+        <v>10.41</v>
       </c>
       <c r="M56" t="n">
         <v>1.33</v>
       </c>
       <c r="N56" t="n">
-        <v>1.31</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="O56" t="n">
         <v>1.67</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3693,6 +4376,14 @@
       <c r="Q57" t="n">
         <v>53</v>
       </c>
+      <c r="R57" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8651,7 +9342,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8661,7 +9352,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -8671,7 +9362,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8">
@@ -8681,7 +9372,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -8691,7 +9382,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93.5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -8701,7 +9392,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168.8</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="11">
@@ -8741,7 +9432,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.24</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="15">
@@ -8751,7 +9442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.43</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="16">
@@ -8761,7 +9452,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="17">
@@ -8771,7 +9462,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64.04000000000001</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="18">
@@ -8781,7 +9472,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.7</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="19">
@@ -8791,7 +9482,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.37</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -8801,7 +9492,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.62</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="21">
@@ -8811,7 +9502,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="22">
@@ -8821,7 +9512,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -8831,7 +9522,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -8841,7 +9532,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="25">
@@ -8861,7 +9552,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.54</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="27">
@@ -8881,7 +9572,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
